--- a/college-posters/data/字段表_第二批.xlsx
+++ b/college-posters/data/字段表_第二批.xlsx
@@ -444,7 +444,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D54"/>
+  <dimension ref="A1:D51"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="16" customWidth="1" min="1" max="1"/>
@@ -659,17 +659,17 @@
       </c>
       <c r="B10" s="2" t="inlineStr">
         <is>
-          <t>深造率</t>
+          <t>就业方向</t>
         </is>
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
-          <t>未查到本科深造率；仅有2024届初次就业落实率98.61%（第三方，不等于深造率）</t>
+          <t>航天科技集团、航天科工集团、中国核工业集团</t>
         </is>
       </c>
       <c r="D10" s="3" t="inlineStr">
         <is>
-          <t>待补（海报暂显示“待补”）</t>
+          <t>待核就业质量报告</t>
         </is>
       </c>
     </row>
@@ -681,17 +681,17 @@
       </c>
       <c r="B11" s="2" t="inlineStr">
         <is>
-          <t>就业方向</t>
+          <t>校园风物</t>
         </is>
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>航天与国防院所、电子信息与互联网、高端装备制造</t>
+          <t>主楼：一校区苏式风格标志建筑；哈工大博物馆：展示航天与学科成果；威海校区：依山傍海的海滨校区</t>
         </is>
       </c>
       <c r="D11" s="3" t="inlineStr">
         <is>
-          <t>待核就业质量报告</t>
+          <t>待核官网介绍</t>
         </is>
       </c>
     </row>
@@ -703,39 +703,39 @@
       </c>
       <c r="B12" s="2" t="inlineStr">
         <is>
-          <t>校园风物</t>
+          <t>选科要求</t>
         </is>
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>主楼：一校区苏式风格标志建筑；哈工大博物馆：展示航天与学科成果；威海校区：依山傍海的海滨校区</t>
+          <t>理工类专业：物理 + 化学；人文社科类：要求较宽，以当年招生章程为准</t>
         </is>
       </c>
       <c r="D12" s="3" t="inlineStr">
         <is>
-          <t>待核官网介绍</t>
+          <t>待核2027年招生章程</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="2" t="inlineStr">
         <is>
-          <t>哈尔滨工业大学</t>
+          <t>中山大学</t>
         </is>
       </c>
       <c r="B13" s="2" t="inlineStr">
         <is>
-          <t>选科要求</t>
+          <t>王牌专业</t>
         </is>
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>理工类专业：物理 + 化学；人文社科类：要求较宽，以当年招生章程为准</t>
+          <t>临床医学、数学与应用数学、化学、生物科学、工商管理、计算机科学与技术</t>
         </is>
       </c>
       <c r="D13" s="3" t="inlineStr">
         <is>
-          <t>待核2027年招生章程</t>
+          <t>待核当年招生专业目录</t>
         </is>
       </c>
     </row>
@@ -747,17 +747,17 @@
       </c>
       <c r="B14" s="2" t="inlineStr">
         <is>
-          <t>王牌专业</t>
+          <t>就业方向</t>
         </is>
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
-          <t>临床医学、数学与应用数学、化学、生物科学、工商管理、计算机科学与技术</t>
+          <t>华为、中广核、南方电网</t>
         </is>
       </c>
       <c r="D14" s="3" t="inlineStr">
         <is>
-          <t>待核当年招生专业目录</t>
+          <t>待核就业质量报告</t>
         </is>
       </c>
     </row>
@@ -769,17 +769,17 @@
       </c>
       <c r="B15" s="2" t="inlineStr">
         <is>
-          <t>深造率</t>
+          <t>知名校友</t>
         </is>
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>未查到全校本科深造率（医学院2023届超80%，仅学院口径）</t>
+          <t>罗俊（1985年获中山大学理学硕士）；许宁生（中山大学物理系校友）；黄达人（中山大学数学系校友、原校长）</t>
         </is>
       </c>
       <c r="D15" s="3" t="inlineStr">
         <is>
-          <t>待补（海报暂显示“待补”）</t>
+          <t>待核（许宁生、黄达人学籍）</t>
         </is>
       </c>
     </row>
@@ -791,17 +791,17 @@
       </c>
       <c r="B16" s="2" t="inlineStr">
         <is>
-          <t>就业方向</t>
+          <t>校园风物</t>
         </is>
       </c>
       <c r="C16" s="2" t="inlineStr">
         <is>
-          <t>医疗卫生、金融与互联网、大湾区科技企业</t>
+          <t>怀士堂：孙中山曾在此发表演讲；康乐园红楼：原岭南大学近代建筑群；珠海校区：依山傍海的校区</t>
         </is>
       </c>
       <c r="D16" s="3" t="inlineStr">
         <is>
-          <t>待核就业质量报告</t>
+          <t>待核官网介绍</t>
         </is>
       </c>
     </row>
@@ -813,61 +813,61 @@
       </c>
       <c r="B17" s="2" t="inlineStr">
         <is>
-          <t>知名校友</t>
+          <t>选科要求</t>
         </is>
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>罗俊（1985年获中山大学理学硕士）；许宁生（中山大学物理系校友）；黄达人（中山大学数学系校友、原校长）</t>
+          <t>理工医类专业：物理 + 化学；人文社科类：要求较宽，以当年招生章程为准</t>
         </is>
       </c>
       <c r="D17" s="3" t="inlineStr">
         <is>
-          <t>待核（许宁生、黄达人学籍）</t>
+          <t>待核2027年招生章程</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" s="2" t="inlineStr">
         <is>
-          <t>中山大学</t>
+          <t>东南大学</t>
         </is>
       </c>
       <c r="B18" s="2" t="inlineStr">
         <is>
-          <t>校园风物</t>
+          <t>QS世界大学排名</t>
         </is>
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
-          <t>怀士堂：孙中山曾在此发表演讲；康乐园红楼：原岭南大学近代建筑群；珠海校区：依山傍海的校区</t>
+          <t>QS 2027 第=335名（2026年251–300区间）</t>
         </is>
       </c>
       <c r="D18" s="3" t="inlineStr">
         <is>
-          <t>待核官网介绍</t>
+          <t>待核QS官网（仅单一来源）</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" s="2" t="inlineStr">
         <is>
-          <t>中山大学</t>
+          <t>东南大学</t>
         </is>
       </c>
       <c r="B19" s="2" t="inlineStr">
         <is>
-          <t>选科要求</t>
+          <t>第4张排名卡</t>
         </is>
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>理工医类专业：物理 + 化学；人文社科类：要求较宽，以当年招生章程为准</t>
+          <t>第二轮双一流建设学科12个（第三方逐项计数）</t>
         </is>
       </c>
       <c r="D19" s="3" t="inlineStr">
         <is>
-          <t>待核2027年招生章程</t>
+          <t>待核教育部名单原文</t>
         </is>
       </c>
     </row>
@@ -879,17 +879,17 @@
       </c>
       <c r="B20" s="2" t="inlineStr">
         <is>
-          <t>QS世界大学排名</t>
+          <t>王牌专业</t>
         </is>
       </c>
       <c r="C20" s="2" t="inlineStr">
         <is>
-          <t>QS 2027 第=335名（2026年251–300区间）</t>
+          <t>建筑学、土木工程、交通工程、电子科学与技术、信息工程、生物医学工程</t>
         </is>
       </c>
       <c r="D20" s="3" t="inlineStr">
         <is>
-          <t>待核QS官网（仅单一来源）</t>
+          <t>待核当年招生专业目录</t>
         </is>
       </c>
     </row>
@@ -901,17 +901,17 @@
       </c>
       <c r="B21" s="2" t="inlineStr">
         <is>
-          <t>第4张排名卡</t>
+          <t>深造率</t>
         </is>
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>第二轮双一流建设学科12个（第三方逐项计数）</t>
+          <t>B方案：学校招生宣传称近年毕业生去往华为、国家电网等重要行业和领域就业的比例高达80%（非单届统计）；中国电科为2025春招重点单位</t>
         </is>
       </c>
       <c r="D21" s="3" t="inlineStr">
         <is>
-          <t>待核教育部名单原文</t>
+          <t>待核（学校宣传口径）</t>
         </is>
       </c>
     </row>
@@ -923,17 +923,17 @@
       </c>
       <c r="B22" s="2" t="inlineStr">
         <is>
-          <t>王牌专业</t>
+          <t>就业方向</t>
         </is>
       </c>
       <c r="C22" s="2" t="inlineStr">
         <is>
-          <t>建筑学、土木工程、交通工程、电子科学与技术、信息工程、生物医学工程</t>
+          <t>华为、国家电网、中国电科</t>
         </is>
       </c>
       <c r="D22" s="3" t="inlineStr">
         <is>
-          <t>待核当年招生专业目录</t>
+          <t>待核就业质量报告</t>
         </is>
       </c>
     </row>
@@ -945,17 +945,17 @@
       </c>
       <c r="B23" s="2" t="inlineStr">
         <is>
-          <t>深造率</t>
+          <t>校园风物</t>
         </is>
       </c>
       <c r="C23" s="2" t="inlineStr">
         <is>
-          <t>未查到2024/2025届本科深造率（2021届为58.79%，过旧未采用）</t>
+          <t>大礼堂：四牌楼校区标志，原中央大学礼堂；六朝松：校园里的千年古柏；九龙湖校区：江宁主校区</t>
         </is>
       </c>
       <c r="D23" s="3" t="inlineStr">
         <is>
-          <t>待补（海报暂显示“待补”）</t>
+          <t>待核官网介绍</t>
         </is>
       </c>
     </row>
@@ -967,61 +967,61 @@
       </c>
       <c r="B24" s="2" t="inlineStr">
         <is>
-          <t>就业方向</t>
+          <t>选科要求</t>
         </is>
       </c>
       <c r="C24" s="2" t="inlineStr">
         <is>
-          <t>电子信息与通信、建筑设计与工程、交通与电力</t>
+          <t>理工类专业：物理 + 化学；人文社科类：要求较宽，以当年招生章程为准</t>
         </is>
       </c>
       <c r="D24" s="3" t="inlineStr">
         <is>
-          <t>待核就业质量报告</t>
+          <t>待核2027年招生章程</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" s="2" t="inlineStr">
         <is>
-          <t>东南大学</t>
+          <t>四川大学</t>
         </is>
       </c>
       <c r="B25" s="2" t="inlineStr">
         <is>
-          <t>校园风物</t>
+          <t>第4张排名卡</t>
         </is>
       </c>
       <c r="C25" s="2" t="inlineStr">
         <is>
-          <t>大礼堂：四牌楼校区标志，原中央大学礼堂；六朝松：校园里的千年古柏；九龙湖校区：江宁主校区</t>
+          <t>第二轮双一流建设学科6个（第三方逐项计数）</t>
         </is>
       </c>
       <c r="D25" s="3" t="inlineStr">
         <is>
-          <t>待核官网介绍</t>
+          <t>待核教育部名单原文</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" s="2" t="inlineStr">
         <is>
-          <t>东南大学</t>
+          <t>四川大学</t>
         </is>
       </c>
       <c r="B26" s="2" t="inlineStr">
         <is>
-          <t>选科要求</t>
+          <t>王牌专业</t>
         </is>
       </c>
       <c r="C26" s="2" t="inlineStr">
         <is>
-          <t>理工类专业：物理 + 化学；人文社科类：要求较宽，以当年招生章程为准</t>
+          <t>口腔医学、临床医学、数学与应用数学、化学、材料科学与工程、汉语言文学</t>
         </is>
       </c>
       <c r="D26" s="3" t="inlineStr">
         <is>
-          <t>待核2027年招生章程</t>
+          <t>待核当年招生专业目录</t>
         </is>
       </c>
     </row>
@@ -1033,17 +1033,17 @@
       </c>
       <c r="B27" s="2" t="inlineStr">
         <is>
-          <t>第4张排名卡</t>
+          <t>深造率</t>
         </is>
       </c>
       <c r="C27" s="2" t="inlineStr">
         <is>
-          <t>第二轮双一流建设学科6个（第三方逐项计数）</t>
+          <t>B方案：多篇文章称超过55%毕业生留在西部、约43%留在成都；2021届官方报告西部就业约六成；成飞、华为、国家电网、华西医院为重点招聘单位</t>
         </is>
       </c>
       <c r="D27" s="3" t="inlineStr">
         <is>
-          <t>待核教育部名单原文</t>
+          <t>待核（第三方口径）</t>
         </is>
       </c>
     </row>
@@ -1055,17 +1055,17 @@
       </c>
       <c r="B28" s="2" t="inlineStr">
         <is>
-          <t>王牌专业</t>
+          <t>就业方向</t>
         </is>
       </c>
       <c r="C28" s="2" t="inlineStr">
         <is>
-          <t>口腔医学、临床医学、数学与应用数学、化学、材料科学与工程、汉语言文学</t>
+          <t>华西医院、成飞、国家电网</t>
         </is>
       </c>
       <c r="D28" s="3" t="inlineStr">
         <is>
-          <t>待核当年招生专业目录</t>
+          <t>待核就业质量报告</t>
         </is>
       </c>
     </row>
@@ -1077,17 +1077,17 @@
       </c>
       <c r="B29" s="2" t="inlineStr">
         <is>
-          <t>深造率</t>
+          <t>校园风物</t>
         </is>
       </c>
       <c r="C29" s="2" t="inlineStr">
         <is>
-          <t>未查到2024/2025届本科深造率</t>
+          <t>华西钟楼：华西坝百年钟楼；明远湖：江安校区中心湖；望江校区：锦江之滨的老校区</t>
         </is>
       </c>
       <c r="D29" s="3" t="inlineStr">
         <is>
-          <t>待补（海报暂显示“待补”）</t>
+          <t>待核官网介绍</t>
         </is>
       </c>
     </row>
@@ -1099,61 +1099,61 @@
       </c>
       <c r="B30" s="2" t="inlineStr">
         <is>
-          <t>就业方向</t>
+          <t>选科要求</t>
         </is>
       </c>
       <c r="C30" s="2" t="inlineStr">
         <is>
-          <t>医疗卫生、电子信息与制造、党政机关与国企</t>
+          <t>理工医类专业：物理 + 化学；人文社科类：要求较宽，以当年招生章程为准</t>
         </is>
       </c>
       <c r="D30" s="3" t="inlineStr">
         <is>
-          <t>待核就业质量报告</t>
+          <t>待核2027年招生章程</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" s="2" t="inlineStr">
         <is>
-          <t>四川大学</t>
+          <t>中国人民大学</t>
         </is>
       </c>
       <c r="B31" s="2" t="inlineStr">
         <is>
-          <t>校园风物</t>
+          <t>王牌专业</t>
         </is>
       </c>
       <c r="C31" s="2" t="inlineStr">
         <is>
-          <t>华西钟楼：华西坝百年钟楼；明远湖：江安校区中心湖；望江校区：锦江之滨的老校区</t>
+          <t>经济学、金融学、法学、新闻学、统计学、工商管理</t>
         </is>
       </c>
       <c r="D31" s="3" t="inlineStr">
         <is>
-          <t>待核官网介绍</t>
+          <t>待核当年招生专业目录</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" s="2" t="inlineStr">
         <is>
-          <t>四川大学</t>
+          <t>中国人民大学</t>
         </is>
       </c>
       <c r="B32" s="2" t="inlineStr">
         <is>
-          <t>选科要求</t>
+          <t>就业方向</t>
         </is>
       </c>
       <c r="C32" s="2" t="inlineStr">
         <is>
-          <t>理工医类专业：物理 + 化学；人文社科类：要求较宽，以当年招生章程为准</t>
+          <t>外交部等党政机关、工商银行、中国银行、大型国企与知名民企</t>
         </is>
       </c>
       <c r="D32" s="3" t="inlineStr">
         <is>
-          <t>待核2027年招生章程</t>
+          <t>待核就业质量报告</t>
         </is>
       </c>
     </row>
@@ -1165,17 +1165,17 @@
       </c>
       <c r="B33" s="2" t="inlineStr">
         <is>
-          <t>王牌专业</t>
+          <t>校园风物</t>
         </is>
       </c>
       <c r="C33" s="2" t="inlineStr">
         <is>
-          <t>经济学、金融学、法学、新闻学、统计学、工商管理</t>
+          <t>实事求是石：刻有校训的标志石；明德楼：人大标志性建筑群；通州校区：城市副中心新校区</t>
         </is>
       </c>
       <c r="D33" s="3" t="inlineStr">
         <is>
-          <t>待核当年招生专业目录</t>
+          <t>待核官网介绍</t>
         </is>
       </c>
     </row>
@@ -1187,83 +1187,83 @@
       </c>
       <c r="B34" s="2" t="inlineStr">
         <is>
-          <t>深造率</t>
+          <t>选科要求</t>
         </is>
       </c>
       <c r="C34" s="2" t="inlineStr">
         <is>
-          <t>未查到2024/2025届本科深造率（境外留学率曾超30%，年份不明）</t>
+          <t>理工类专业：物理 + 化学；人文社科类：要求较宽，以当年招生章程为准</t>
         </is>
       </c>
       <c r="D34" s="3" t="inlineStr">
         <is>
-          <t>待补（海报暂显示“待补”）</t>
+          <t>待核2027年招生章程</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" s="2" t="inlineStr">
         <is>
-          <t>中国人民大学</t>
+          <t>同济大学</t>
         </is>
       </c>
       <c r="B35" s="2" t="inlineStr">
         <is>
-          <t>就业方向</t>
+          <t>第4张排名卡</t>
         </is>
       </c>
       <c r="C35" s="2" t="inlineStr">
         <is>
-          <t>金融与经济、党政机关、法律与传媒</t>
+          <t>第二轮双一流建设学科8个（第三方逐项计数）</t>
         </is>
       </c>
       <c r="D35" s="3" t="inlineStr">
         <is>
-          <t>待核就业质量报告</t>
+          <t>待核教育部名单原文</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" s="2" t="inlineStr">
         <is>
-          <t>中国人民大学</t>
+          <t>同济大学</t>
         </is>
       </c>
       <c r="B36" s="2" t="inlineStr">
         <is>
-          <t>校园风物</t>
+          <t>王牌专业</t>
         </is>
       </c>
       <c r="C36" s="2" t="inlineStr">
         <is>
-          <t>实事求是石：刻有校训的标志石；明德楼：人大标志性建筑群；通州校区：城市副中心新校区</t>
+          <t>建筑学、城乡规划、土木工程、车辆工程、环境工程、工业设计</t>
         </is>
       </c>
       <c r="D36" s="3" t="inlineStr">
         <is>
-          <t>待核官网介绍</t>
+          <t>待核当年招生专业目录</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" s="2" t="inlineStr">
         <is>
-          <t>中国人民大学</t>
+          <t>同济大学</t>
         </is>
       </c>
       <c r="B37" s="2" t="inlineStr">
         <is>
-          <t>选科要求</t>
+          <t>就业方向</t>
         </is>
       </c>
       <c r="C37" s="2" t="inlineStr">
         <is>
-          <t>理工类专业：物理 + 化学；人文社科类：要求较宽，以当年招生章程为准</t>
+          <t>建筑设计与城市规划、土木交通工程、汽车与先进制造</t>
         </is>
       </c>
       <c r="D37" s="3" t="inlineStr">
         <is>
-          <t>待核2027年招生章程</t>
+          <t>待核就业质量报告</t>
         </is>
       </c>
     </row>
@@ -1275,17 +1275,17 @@
       </c>
       <c r="B38" s="2" t="inlineStr">
         <is>
-          <t>第4张排名卡</t>
+          <t>校园风物</t>
         </is>
       </c>
       <c r="C38" s="2" t="inlineStr">
         <is>
-          <t>第二轮双一流建设学科8个（第三方逐项计数）</t>
+          <t>文远楼（1953年建，常被称为中国第一座包豪斯风格建筑）；大礼堂（1962年建，大跨度拱形结构）</t>
         </is>
       </c>
       <c r="D38" s="3" t="inlineStr">
         <is>
-          <t>待核教育部名单原文</t>
+          <t>待核官网介绍</t>
         </is>
       </c>
     </row>
@@ -1297,83 +1297,83 @@
       </c>
       <c r="B39" s="2" t="inlineStr">
         <is>
-          <t>王牌专业</t>
+          <t>选科要求</t>
         </is>
       </c>
       <c r="C39" s="2" t="inlineStr">
         <is>
-          <t>建筑学、城乡规划、土木工程、车辆工程、环境工程、工业设计</t>
+          <t>理工类专业：物理 + 化学；人文社科类：要求较宽，以当年招生章程为准</t>
         </is>
       </c>
       <c r="D39" s="3" t="inlineStr">
         <is>
-          <t>待核当年招生专业目录</t>
+          <t>待核2027年招生章程</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" s="2" t="inlineStr">
         <is>
-          <t>同济大学</t>
+          <t>北京师范大学</t>
         </is>
       </c>
       <c r="B40" s="2" t="inlineStr">
         <is>
-          <t>就业方向</t>
+          <t>王牌专业</t>
         </is>
       </c>
       <c r="C40" s="2" t="inlineStr">
         <is>
-          <t>建筑设计与城市规划、土木交通工程、汽车与先进制造</t>
+          <t>教育学、心理学、汉语言文学、数学与应用数学、地理科学、戏剧影视文学</t>
         </is>
       </c>
       <c r="D40" s="3" t="inlineStr">
         <is>
-          <t>待核就业质量报告</t>
+          <t>待核当年招生专业目录</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" s="2" t="inlineStr">
         <is>
-          <t>同济大学</t>
+          <t>北京师范大学</t>
         </is>
       </c>
       <c r="B41" s="2" t="inlineStr">
         <is>
-          <t>校园风物</t>
+          <t>就业方向</t>
         </is>
       </c>
       <c r="C41" s="2" t="inlineStr">
         <is>
-          <t>文远楼（1953年建，常被称为中国第一座包豪斯风格建筑）；大礼堂（1962年建，大跨度拱形结构）</t>
+          <t>教育与科研、文化传媒、党政机关与国企</t>
         </is>
       </c>
       <c r="D41" s="3" t="inlineStr">
         <is>
-          <t>待核官网介绍</t>
+          <t>待核就业质量报告</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" s="2" t="inlineStr">
         <is>
-          <t>同济大学</t>
+          <t>北京师范大学</t>
         </is>
       </c>
       <c r="B42" s="2" t="inlineStr">
         <is>
-          <t>选科要求</t>
+          <t>校园风物</t>
         </is>
       </c>
       <c r="C42" s="2" t="inlineStr">
         <is>
-          <t>理工类专业：物理 + 化学；人文社科类：要求较宽，以当年招生章程为准</t>
+          <t>木铎：校园标志，寓意教化；主楼：北京校区地标建筑；珠海校区：南国海滨的校区</t>
         </is>
       </c>
       <c r="D42" s="3" t="inlineStr">
         <is>
-          <t>待核2027年招生章程</t>
+          <t>待核官网介绍</t>
         </is>
       </c>
     </row>
@@ -1385,83 +1385,83 @@
       </c>
       <c r="B43" s="2" t="inlineStr">
         <is>
-          <t>王牌专业</t>
+          <t>选科要求</t>
         </is>
       </c>
       <c r="C43" s="2" t="inlineStr">
         <is>
-          <t>教育学、心理学、汉语言文学、数学与应用数学、地理科学、戏剧影视文学</t>
+          <t>理工类专业：物理 + 化学；人文社科类：要求较宽，以当年招生章程为准</t>
         </is>
       </c>
       <c r="D43" s="3" t="inlineStr">
         <is>
-          <t>待核当年招生专业目录</t>
+          <t>待核2027年招生章程</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" s="2" t="inlineStr">
         <is>
-          <t>北京师范大学</t>
+          <t>天津大学</t>
         </is>
       </c>
       <c r="B44" s="2" t="inlineStr">
         <is>
-          <t>就业方向</t>
+          <t>王牌专业</t>
         </is>
       </c>
       <c r="C44" s="2" t="inlineStr">
         <is>
-          <t>教育与科研、文化传媒、党政机关与国企</t>
+          <t>化学工程与工艺、建筑学、测控技术与仪器、材料科学与工程、能源与动力工程、港口航道与海岸工程</t>
         </is>
       </c>
       <c r="D44" s="3" t="inlineStr">
         <is>
-          <t>待核就业质量报告</t>
+          <t>待核当年招生专业目录</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" s="2" t="inlineStr">
         <is>
-          <t>北京师范大学</t>
+          <t>天津大学</t>
         </is>
       </c>
       <c r="B45" s="2" t="inlineStr">
         <is>
-          <t>校园风物</t>
+          <t>就业方向</t>
         </is>
       </c>
       <c r="C45" s="2" t="inlineStr">
         <is>
-          <t>木铎：校园标志，寓意教化；主楼：北京校区地标建筑；珠海校区：南国海滨的校区</t>
+          <t>化工与能源、建筑与土木工程、电子信息与制造</t>
         </is>
       </c>
       <c r="D45" s="3" t="inlineStr">
         <is>
-          <t>待核官网介绍</t>
+          <t>待核就业质量报告</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" s="2" t="inlineStr">
         <is>
-          <t>北京师范大学</t>
+          <t>天津大学</t>
         </is>
       </c>
       <c r="B46" s="2" t="inlineStr">
         <is>
-          <t>选科要求</t>
+          <t>校园风物</t>
         </is>
       </c>
       <c r="C46" s="2" t="inlineStr">
         <is>
-          <t>理工类专业：物理 + 化学；人文社科类：要求较宽，以当年招生章程为准</t>
+          <t>北洋园校区：海河教育园区新校区；敬业湖：卫津路校区中心湖；卫津路校区：与南开大学一路之隔</t>
         </is>
       </c>
       <c r="D46" s="3" t="inlineStr">
         <is>
-          <t>待核2027年招生章程</t>
+          <t>待核官网介绍</t>
         </is>
       </c>
     </row>
@@ -1473,83 +1473,83 @@
       </c>
       <c r="B47" s="2" t="inlineStr">
         <is>
-          <t>王牌专业</t>
+          <t>选科要求</t>
         </is>
       </c>
       <c r="C47" s="2" t="inlineStr">
         <is>
-          <t>化学工程与工艺、建筑学、测控技术与仪器、材料科学与工程、能源与动力工程、港口航道与海岸工程</t>
+          <t>理工类专业：物理 + 化学；人文社科类：要求较宽，以当年招生章程为准</t>
         </is>
       </c>
       <c r="D47" s="3" t="inlineStr">
         <is>
-          <t>待核当年招生专业目录</t>
+          <t>待核2027年招生章程</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" s="2" t="inlineStr">
         <is>
-          <t>天津大学</t>
+          <t>南开大学</t>
         </is>
       </c>
       <c r="B48" s="2" t="inlineStr">
         <is>
-          <t>就业方向</t>
+          <t>王牌专业</t>
         </is>
       </c>
       <c r="C48" s="2" t="inlineStr">
         <is>
-          <t>化工与能源、建筑与土木工程、电子信息与制造</t>
+          <t>数学与应用数学、化学、统计学、金融学、经济学、历史学</t>
         </is>
       </c>
       <c r="D48" s="3" t="inlineStr">
         <is>
-          <t>待核就业质量报告</t>
+          <t>待核当年招生专业目录</t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="A49" s="2" t="inlineStr">
         <is>
-          <t>天津大学</t>
+          <t>南开大学</t>
         </is>
       </c>
       <c r="B49" s="2" t="inlineStr">
         <is>
-          <t>校园风物</t>
+          <t>就业方向</t>
         </is>
       </c>
       <c r="C49" s="2" t="inlineStr">
         <is>
-          <t>北洋园校区：海河教育园区新校区；敬业湖：卫津路校区中心湖；卫津路校区：与南开大学一路之隔</t>
+          <t>金融与经济、科研院所与高校、党政机关与国企</t>
         </is>
       </c>
       <c r="D49" s="3" t="inlineStr">
         <is>
-          <t>待核官网介绍</t>
+          <t>待核就业质量报告</t>
         </is>
       </c>
     </row>
     <row r="50">
       <c r="A50" s="2" t="inlineStr">
         <is>
-          <t>天津大学</t>
+          <t>南开大学</t>
         </is>
       </c>
       <c r="B50" s="2" t="inlineStr">
         <is>
-          <t>选科要求</t>
+          <t>校园风物</t>
         </is>
       </c>
       <c r="C50" s="2" t="inlineStr">
         <is>
-          <t>理工类专业：物理 + 化学；人文社科类：要求较宽，以当年招生章程为准</t>
+          <t>马蹄湖：湖畔立有周恩来总理像；新开湖：八里台校区中心湖；津南校区：海河教育园区新校区</t>
         </is>
       </c>
       <c r="D50" s="3" t="inlineStr">
         <is>
-          <t>待核2027年招生章程</t>
+          <t>待核官网介绍</t>
         </is>
       </c>
     </row>
@@ -1561,81 +1561,15 @@
       </c>
       <c r="B51" s="2" t="inlineStr">
         <is>
-          <t>王牌专业</t>
+          <t>选科要求</t>
         </is>
       </c>
       <c r="C51" s="2" t="inlineStr">
         <is>
-          <t>数学与应用数学、化学、统计学、金融学、经济学、历史学</t>
+          <t>理工类专业：物理 + 化学；人文社科类：要求较宽，以当年招生章程为准</t>
         </is>
       </c>
       <c r="D51" s="3" t="inlineStr">
-        <is>
-          <t>待核当年招生专业目录</t>
-        </is>
-      </c>
-    </row>
-    <row r="52">
-      <c r="A52" s="2" t="inlineStr">
-        <is>
-          <t>南开大学</t>
-        </is>
-      </c>
-      <c r="B52" s="2" t="inlineStr">
-        <is>
-          <t>就业方向</t>
-        </is>
-      </c>
-      <c r="C52" s="2" t="inlineStr">
-        <is>
-          <t>金融与经济、科研院所与高校、党政机关与国企</t>
-        </is>
-      </c>
-      <c r="D52" s="3" t="inlineStr">
-        <is>
-          <t>待核就业质量报告</t>
-        </is>
-      </c>
-    </row>
-    <row r="53">
-      <c r="A53" s="2" t="inlineStr">
-        <is>
-          <t>南开大学</t>
-        </is>
-      </c>
-      <c r="B53" s="2" t="inlineStr">
-        <is>
-          <t>校园风物</t>
-        </is>
-      </c>
-      <c r="C53" s="2" t="inlineStr">
-        <is>
-          <t>马蹄湖：湖畔立有周恩来总理像；新开湖：八里台校区中心湖；津南校区：海河教育园区新校区</t>
-        </is>
-      </c>
-      <c r="D53" s="3" t="inlineStr">
-        <is>
-          <t>待核官网介绍</t>
-        </is>
-      </c>
-    </row>
-    <row r="54">
-      <c r="A54" s="2" t="inlineStr">
-        <is>
-          <t>南开大学</t>
-        </is>
-      </c>
-      <c r="B54" s="2" t="inlineStr">
-        <is>
-          <t>选科要求</t>
-        </is>
-      </c>
-      <c r="C54" s="2" t="inlineStr">
-        <is>
-          <t>理工类专业：物理 + 化学；人文社科类：要求较宽，以当年招生章程为准</t>
-        </is>
-      </c>
-      <c r="D54" s="3" t="inlineStr">
         <is>
           <t>待核2027年招生章程</t>
         </is>
@@ -1873,7 +1807,7 @@
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>20名</t>
+          <t>20名（2026）</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
@@ -1905,7 +1839,7 @@
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
-          <t>235名</t>
+          <t>235名（2027）</t>
         </is>
       </c>
       <c r="E8" s="2" t="inlineStr">
@@ -1937,7 +1871,7 @@
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>98名</t>
+          <t>98名（2026）</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
@@ -2631,7 +2565,7 @@
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>21名</t>
+          <t>21名（2026）</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
@@ -2663,7 +2597,7 @@
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
-          <t>329名</t>
+          <t>329名（2027）</t>
         </is>
       </c>
       <c r="E8" s="2" t="inlineStr">
@@ -2695,7 +2629,7 @@
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>101-150名</t>
+          <t>101-150（2026）</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
@@ -3389,7 +3323,7 @@
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>11名</t>
+          <t>11名（2026）</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
@@ -3421,7 +3355,7 @@
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
-          <t>349名</t>
+          <t>349名（2027）</t>
         </is>
       </c>
       <c r="E8" s="2" t="inlineStr">
@@ -3453,7 +3387,7 @@
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>101-150名</t>
+          <t>101-150（2026）</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
@@ -4147,7 +4081,7 @@
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>12名</t>
+          <t>12名（2026）</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
@@ -4179,7 +4113,7 @@
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
-          <t>190名</t>
+          <t>190名（2027）</t>
         </is>
       </c>
       <c r="E8" s="2" t="inlineStr">
@@ -4211,7 +4145,7 @@
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>97名</t>
+          <t>97名（2026）</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
@@ -4430,22 +4364,22 @@
       </c>
       <c r="C16" s="2" t="inlineStr">
         <is>
-          <t>未查到本科深造率；仅有2024届初次就业落实率98.61%（第三方，不等于深造率）</t>
-        </is>
-      </c>
-      <c r="D16" s="3" t="inlineStr">
-        <is>
-          <t>待补（核实中）</t>
+          <t>未查到本科深造率；B方案改放2024届初次去向落实率98.61%（落实去向3916人）；主要去向中核集团、航天科技、航天科工、航空工业，航天就业人数增长119.46%</t>
+        </is>
+      </c>
+      <c r="D16" s="2" t="inlineStr">
+        <is>
+          <t>98.61%（2024届）</t>
         </is>
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>哈工大2023-2024学年本科教学质量报告（官网PDF未能直连）</t>
-        </is>
-      </c>
-      <c r="F16" s="3" t="inlineStr">
-        <is>
-          <t>待补（海报暂显示“待补”）</t>
+          <t>自主选拔在线、大学生必备网转载</t>
+        </is>
+      </c>
+      <c r="F16" s="2" t="inlineStr">
+        <is>
+          <t>较可靠（转载，非深造率）</t>
         </is>
       </c>
     </row>
@@ -4462,7 +4396,7 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>航天与国防院所、电子信息与互联网、高端装备制造</t>
+          <t>航天科技集团、航天科工集团、中国核工业集团</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
@@ -4905,7 +4839,7 @@
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>13名</t>
+          <t>13名（2026）</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
@@ -4937,7 +4871,7 @@
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
-          <t>258名</t>
+          <t>258名（2027）</t>
         </is>
       </c>
       <c r="E8" s="2" t="inlineStr">
@@ -4969,7 +4903,7 @@
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>62名</t>
+          <t>62名（2026）</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
@@ -5188,22 +5122,22 @@
       </c>
       <c r="C16" s="2" t="inlineStr">
         <is>
-          <t>未查到全校本科深造率（医学院2023届超80%，仅学院口径）</t>
-        </is>
-      </c>
-      <c r="D16" s="3" t="inlineStr">
-        <is>
-          <t>待补（核实中）</t>
+          <t>B方案：校长高松2026年全国两会公开表示，中大70%以上2025届毕业生留在广东工作；签约企业华为、中广核、南方电网来自第三方文章</t>
+        </is>
+      </c>
+      <c r="D16" s="2" t="inlineStr">
+        <is>
+          <t>70%+（2025届）</t>
         </is>
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>中山大学2023-2024学年本科教学质量报告（官网PDF未能直连）</t>
-        </is>
-      </c>
-      <c r="F16" s="3" t="inlineStr">
-        <is>
-          <t>待补（海报暂显示“待补”）</t>
+          <t>羊城晚报等报道；网易转载</t>
+        </is>
+      </c>
+      <c r="F16" s="2" t="inlineStr">
+        <is>
+          <t>已核（70%+）；签约单位待核</t>
         </is>
       </c>
     </row>
@@ -5220,7 +5154,7 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>医疗卫生、金融与互联网、大湾区科技企业</t>
+          <t>华为、中广核、南方电网</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
@@ -5663,7 +5597,7 @@
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>15名</t>
+          <t>15名（2026）</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
@@ -5695,7 +5629,7 @@
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
-          <t>335名</t>
+          <t>335名（2027）</t>
         </is>
       </c>
       <c r="E8" s="2" t="inlineStr">
@@ -5727,7 +5661,7 @@
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>89名</t>
+          <t>89名（2026）</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
@@ -5946,22 +5880,22 @@
       </c>
       <c r="C16" s="2" t="inlineStr">
         <is>
-          <t>未查到2024/2025届本科深造率（2021届为58.79%，过旧未采用）</t>
-        </is>
-      </c>
-      <c r="D16" s="3" t="inlineStr">
-        <is>
-          <t>待补（核实中）</t>
+          <t>B方案：学校招生宣传称近年毕业生去往华为、国家电网等重要行业和领域就业的比例高达80%（非单届统计）；中国电科为2025春招重点单位</t>
+        </is>
+      </c>
+      <c r="D16" s="2" t="inlineStr">
+        <is>
+          <t>80%（近年）</t>
         </is>
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>东南大学本科教学质量报告（官网PDF未能直连）</t>
+          <t>扬子晚报《2025上好大学》、东大新闻网</t>
         </is>
       </c>
       <c r="F16" s="3" t="inlineStr">
         <is>
-          <t>待补（海报暂显示“待补”）</t>
+          <t>待核（学校宣传口径）</t>
         </is>
       </c>
     </row>
@@ -5978,7 +5912,7 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>电子信息与通信、建筑设计与工程、交通与电力</t>
+          <t>华为、国家电网、中国电科</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
@@ -6421,7 +6355,7 @@
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>16名</t>
+          <t>16名（2026）</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
@@ -6453,7 +6387,7 @@
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
-          <t>300名</t>
+          <t>300名（2027）</t>
         </is>
       </c>
       <c r="E8" s="2" t="inlineStr">
@@ -6485,7 +6419,7 @@
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>77名</t>
+          <t>77名（2026）</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
@@ -6704,22 +6638,22 @@
       </c>
       <c r="C16" s="2" t="inlineStr">
         <is>
-          <t>未查到2024/2025届本科深造率</t>
-        </is>
-      </c>
-      <c r="D16" s="3" t="inlineStr">
-        <is>
-          <t>待补（核实中）</t>
+          <t>B方案：多篇文章称超过55%毕业生留在西部、约43%留在成都；2021届官方报告西部就业约六成；成飞、华为、国家电网、华西医院为重点招聘单位</t>
+        </is>
+      </c>
+      <c r="D16" s="2" t="inlineStr">
+        <is>
+          <t>55%+（近年）</t>
         </is>
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>四川大学2023-2024学年本科教学质量报告（官网PDF未能直连）</t>
+          <t>网易等第三方文章；川大2021届就业质量报告</t>
         </is>
       </c>
       <c r="F16" s="3" t="inlineStr">
         <is>
-          <t>待补（海报暂显示“待补”）</t>
+          <t>待核（第三方口径）</t>
         </is>
       </c>
     </row>
@@ -6736,7 +6670,7 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>医疗卫生、电子信息与制造、党政机关与国企</t>
+          <t>华西医院、成飞、国家电网</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
@@ -7179,7 +7113,7 @@
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>17名</t>
+          <t>17名（2026）</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
@@ -7211,7 +7145,7 @@
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
-          <t>521名</t>
+          <t>521名（2027）</t>
         </is>
       </c>
       <c r="E8" s="2" t="inlineStr">
@@ -7243,7 +7177,7 @@
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>9名</t>
+          <t>不放（未查到可靠名次）</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
@@ -7275,7 +7209,7 @@
       </c>
       <c r="D10" s="2" t="inlineStr">
         <is>
-          <t>14个</t>
+          <t>9个；14个</t>
         </is>
       </c>
       <c r="E10" s="2" t="inlineStr">
@@ -7462,22 +7396,22 @@
       </c>
       <c r="C16" s="2" t="inlineStr">
         <is>
-          <t>未查到2024/2025届本科深造率（境外留学率曾超30%，年份不明）</t>
-        </is>
-      </c>
-      <c r="D16" s="3" t="inlineStr">
-        <is>
-          <t>待补（核实中）</t>
+          <t>B方案：不放数字，列2024届直接就业主要去向——外交部等国家党政机关，中国工商银行、中国银行等各大银行，大型国企与知名民企</t>
+        </is>
+      </c>
+      <c r="D16" s="2" t="inlineStr">
+        <is>
+          <t>不放数字</t>
         </is>
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>人大2023-2024学年本科教学质量报告（未能直连）</t>
-        </is>
-      </c>
-      <c r="F16" s="3" t="inlineStr">
-        <is>
-          <t>待补（海报暂显示“待补”）</t>
+          <t>搜狐转载人大2024届就业情况</t>
+        </is>
+      </c>
+      <c r="F16" s="2" t="inlineStr">
+        <is>
+          <t>较可靠（转载）</t>
         </is>
       </c>
     </row>
@@ -7494,7 +7428,7 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>金融与经济、党政机关、法律与传媒</t>
+          <t>外交部等党政机关、工商银行、中国银行、大型国企与知名民企</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
@@ -7937,7 +7871,7 @@
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>18名</t>
+          <t>18名（2026）</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
@@ -7969,7 +7903,7 @@
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
-          <t>146名</t>
+          <t>146名（2027）</t>
         </is>
       </c>
       <c r="E8" s="2" t="inlineStr">
@@ -8001,7 +7935,7 @@
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>101-150名</t>
+          <t>101-150（2026）</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
@@ -8695,7 +8629,7 @@
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>19名</t>
+          <t>19名（2026）</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
@@ -8727,7 +8661,7 @@
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
-          <t>237名</t>
+          <t>237名（2027）</t>
         </is>
       </c>
       <c r="E8" s="2" t="inlineStr">
@@ -8759,7 +8693,7 @@
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>101-150名</t>
+          <t>101-150（2026）</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">

--- a/college-posters/data/字段表_第二批.xlsx
+++ b/college-posters/data/字段表_第二批.xlsx
@@ -444,7 +444,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D51"/>
+  <dimension ref="A1:D24"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="16" customWidth="1" min="1" max="1"/>
@@ -483,17 +483,17 @@
       </c>
       <c r="B2" s="2" t="inlineStr">
         <is>
-          <t>QS世界大学排名</t>
+          <t>王牌专业</t>
         </is>
       </c>
       <c r="C2" s="2" t="inlineStr">
         <is>
-          <t>QS 2027 第=349名（2026年第388名）</t>
+          <t>飞行器设计与工程、航空航天工程、计算机科学与技术、软件工程、自动化、电子信息工程</t>
         </is>
       </c>
       <c r="D2" s="3" t="inlineStr">
         <is>
-          <t>待核QS官网（仅单一来源）</t>
+          <t>待核当年招生专业目录</t>
         </is>
       </c>
     </row>
@@ -505,17 +505,17 @@
       </c>
       <c r="B3" s="2" t="inlineStr">
         <is>
-          <t>王牌专业</t>
+          <t>深造率</t>
         </is>
       </c>
       <c r="C3" s="2" t="inlineStr">
         <is>
-          <t>飞行器设计与工程、航空航天工程、计算机科学与技术、软件工程、自动化、电子信息工程</t>
+          <t>2024届本科毕业生3395人，升学深造率86.92%（2023届为71.78%，两年差距大，口径可能不同）</t>
         </is>
       </c>
       <c r="D3" s="3" t="inlineStr">
         <is>
-          <t>待核当年招生专业目录</t>
+          <t>待核报告原文（与上年差距大）</t>
         </is>
       </c>
     </row>
@@ -527,112 +527,112 @@
       </c>
       <c r="B4" s="2" t="inlineStr">
         <is>
-          <t>深造率</t>
+          <t>校园风物</t>
         </is>
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
-          <t>2024届本科毕业生3395人，升学深造率86.92%（2023届为71.78%，两年差距大，口径可能不同）</t>
+          <t>新主楼：学院路校区地标建筑；航空航天博物馆：馆藏数十架珍贵飞机；沙河校区：昌平沙河高教园区校区</t>
         </is>
       </c>
       <c r="D4" s="3" t="inlineStr">
         <is>
-          <t>待核报告原文（与上年差距大）</t>
+          <t>待核官网介绍</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="2" t="inlineStr">
         <is>
-          <t>北京航空航天大学</t>
+          <t>哈尔滨工业大学</t>
         </is>
       </c>
       <c r="B5" s="2" t="inlineStr">
         <is>
-          <t>就业方向</t>
+          <t>王牌专业</t>
         </is>
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>航空航天科研院所、电子信息与互联网、国防军工企业</t>
+          <t>飞行器设计与工程、机械设计制造及其自动化、自动化、计算机科学与技术、材料成型及控制工程、土木工程</t>
         </is>
       </c>
       <c r="D5" s="3" t="inlineStr">
         <is>
-          <t>待核就业质量报告</t>
+          <t>待核当年招生专业目录</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="2" t="inlineStr">
         <is>
-          <t>北京航空航天大学</t>
+          <t>哈尔滨工业大学</t>
         </is>
       </c>
       <c r="B6" s="2" t="inlineStr">
         <is>
-          <t>知名校友</t>
+          <t>校园风物</t>
         </is>
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>戚发轫（北京航空学院首届学生）；陈懋章（北航首届学生，院士）；罗阳（北京航空学院1982届，歼-15研制现场总指挥）</t>
+          <t>主楼：一校区苏式风格标志建筑；哈工大博物馆：展示航天与学科成果；威海校区：依山傍海的海滨校区</t>
         </is>
       </c>
       <c r="D6" s="3" t="inlineStr">
         <is>
-          <t>待核（罗阳学籍）</t>
+          <t>待核官网介绍</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="2" t="inlineStr">
         <is>
-          <t>北京航空航天大学</t>
+          <t>中山大学</t>
         </is>
       </c>
       <c r="B7" s="2" t="inlineStr">
         <is>
-          <t>校园风物</t>
+          <t>王牌专业</t>
         </is>
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>新主楼：学院路校区地标建筑；航空航天博物馆：馆藏数十架珍贵飞机；沙河校区：昌平沙河高教园区校区</t>
+          <t>临床医学、数学与应用数学、化学、生物科学、工商管理、计算机科学与技术</t>
         </is>
       </c>
       <c r="D7" s="3" t="inlineStr">
         <is>
-          <t>待核官网介绍</t>
+          <t>待核当年招生专业目录</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="2" t="inlineStr">
         <is>
-          <t>北京航空航天大学</t>
+          <t>中山大学</t>
         </is>
       </c>
       <c r="B8" s="2" t="inlineStr">
         <is>
-          <t>选科要求</t>
+          <t>校园风物</t>
         </is>
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
-          <t>理工类专业：物理 + 化学；人文社科类：要求较宽，以当年招生章程为准</t>
+          <t>怀士堂：孙中山曾在此发表演讲；康乐园红楼：原岭南大学近代建筑群；珠海校区：依山傍海的校区</t>
         </is>
       </c>
       <c r="D8" s="3" t="inlineStr">
         <is>
-          <t>待核2027年招生章程</t>
+          <t>待核官网介绍</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="2" t="inlineStr">
         <is>
-          <t>哈尔滨工业大学</t>
+          <t>东南大学</t>
         </is>
       </c>
       <c r="B9" s="2" t="inlineStr">
@@ -642,7 +642,7 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>飞行器设计与工程、机械设计制造及其自动化、自动化、计算机科学与技术、材料成型及控制工程、土木工程</t>
+          <t>建筑学、土木工程、交通工程、电子科学与技术、信息工程、生物医学工程</t>
         </is>
       </c>
       <c r="D9" s="3" t="inlineStr">
@@ -654,29 +654,29 @@
     <row r="10">
       <c r="A10" s="2" t="inlineStr">
         <is>
-          <t>哈尔滨工业大学</t>
+          <t>东南大学</t>
         </is>
       </c>
       <c r="B10" s="2" t="inlineStr">
         <is>
-          <t>就业方向</t>
+          <t>深造率</t>
         </is>
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
-          <t>航天科技集团、航天科工集团、中国核工业集团</t>
+          <t>B方案：学校招生宣传称近年毕业生去往华为、国家电网等重要行业和领域就业的比例高达80%（非单届统计）；中国电科为2025春招重点单位</t>
         </is>
       </c>
       <c r="D10" s="3" t="inlineStr">
         <is>
-          <t>待核就业质量报告</t>
+          <t>待核（学校宣传口径）</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="2" t="inlineStr">
         <is>
-          <t>哈尔滨工业大学</t>
+          <t>东南大学</t>
         </is>
       </c>
       <c r="B11" s="2" t="inlineStr">
@@ -686,7 +686,7 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>主楼：一校区苏式风格标志建筑；哈工大博物馆：展示航天与学科成果；威海校区：依山傍海的海滨校区</t>
+          <t>大礼堂：四牌楼校区标志，原中央大学礼堂；六朝松：校园里的千年古柏；九龙湖校区：江宁主校区</t>
         </is>
       </c>
       <c r="D11" s="3" t="inlineStr">
@@ -698,95 +698,95 @@
     <row r="12">
       <c r="A12" s="2" t="inlineStr">
         <is>
-          <t>哈尔滨工业大学</t>
+          <t>四川大学</t>
         </is>
       </c>
       <c r="B12" s="2" t="inlineStr">
         <is>
-          <t>选科要求</t>
+          <t>王牌专业</t>
         </is>
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>理工类专业：物理 + 化学；人文社科类：要求较宽，以当年招生章程为准</t>
+          <t>口腔医学、临床医学、数学与应用数学、化学、材料科学与工程、汉语言文学</t>
         </is>
       </c>
       <c r="D12" s="3" t="inlineStr">
         <is>
-          <t>待核2027年招生章程</t>
+          <t>待核当年招生专业目录</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="2" t="inlineStr">
         <is>
-          <t>中山大学</t>
+          <t>四川大学</t>
         </is>
       </c>
       <c r="B13" s="2" t="inlineStr">
         <is>
-          <t>王牌专业</t>
+          <t>深造率</t>
         </is>
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>临床医学、数学与应用数学、化学、生物科学、工商管理、计算机科学与技术</t>
+          <t>B方案：多篇文章称超过55%毕业生留在西部、约43%留在成都；2021届官方报告西部就业约六成；成飞、华为、国家电网、华西医院为重点招聘单位</t>
         </is>
       </c>
       <c r="D13" s="3" t="inlineStr">
         <is>
-          <t>待核当年招生专业目录</t>
+          <t>待核（第三方口径）</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="2" t="inlineStr">
         <is>
-          <t>中山大学</t>
+          <t>四川大学</t>
         </is>
       </c>
       <c r="B14" s="2" t="inlineStr">
         <is>
-          <t>就业方向</t>
+          <t>校园风物</t>
         </is>
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
-          <t>华为、中广核、南方电网</t>
+          <t>华西钟楼：华西坝百年钟楼；明远湖：江安校区中心湖；望江校区：锦江之滨的老校区</t>
         </is>
       </c>
       <c r="D14" s="3" t="inlineStr">
         <is>
-          <t>待核就业质量报告</t>
+          <t>待核官网介绍</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="2" t="inlineStr">
         <is>
-          <t>中山大学</t>
+          <t>中国人民大学</t>
         </is>
       </c>
       <c r="B15" s="2" t="inlineStr">
         <is>
-          <t>知名校友</t>
+          <t>王牌专业</t>
         </is>
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>罗俊（1985年获中山大学理学硕士）；许宁生（中山大学物理系校友）；黄达人（中山大学数学系校友、原校长）</t>
+          <t>经济学、金融学、法学、新闻学、统计学、工商管理</t>
         </is>
       </c>
       <c r="D15" s="3" t="inlineStr">
         <is>
-          <t>待核（许宁生、黄达人学籍）</t>
+          <t>待核当年招生专业目录</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="2" t="inlineStr">
         <is>
-          <t>中山大学</t>
+          <t>中国人民大学</t>
         </is>
       </c>
       <c r="B16" s="2" t="inlineStr">
@@ -796,7 +796,7 @@
       </c>
       <c r="C16" s="2" t="inlineStr">
         <is>
-          <t>怀士堂：孙中山曾在此发表演讲；康乐园红楼：原岭南大学近代建筑群；珠海校区：依山傍海的校区</t>
+          <t>实事求是石：刻有校训的标志石；明德楼：人大标志性建筑群；通州校区：城市副中心新校区</t>
         </is>
       </c>
       <c r="D16" s="3" t="inlineStr">
@@ -808,770 +808,176 @@
     <row r="17">
       <c r="A17" s="2" t="inlineStr">
         <is>
-          <t>中山大学</t>
+          <t>同济大学</t>
         </is>
       </c>
       <c r="B17" s="2" t="inlineStr">
         <is>
-          <t>选科要求</t>
+          <t>王牌专业</t>
         </is>
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>理工医类专业：物理 + 化学；人文社科类：要求较宽，以当年招生章程为准</t>
+          <t>建筑学、城乡规划、土木工程、车辆工程、环境工程、工业设计</t>
         </is>
       </c>
       <c r="D17" s="3" t="inlineStr">
         <is>
-          <t>待核2027年招生章程</t>
+          <t>待核当年招生专业目录</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" s="2" t="inlineStr">
         <is>
-          <t>东南大学</t>
+          <t>同济大学</t>
         </is>
       </c>
       <c r="B18" s="2" t="inlineStr">
         <is>
-          <t>QS世界大学排名</t>
+          <t>校园风物</t>
         </is>
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
-          <t>QS 2027 第=335名（2026年251–300区间）</t>
+          <t>文远楼（1953年建，常被称为中国第一座包豪斯风格建筑）；大礼堂（1962年建，大跨度拱形结构）</t>
         </is>
       </c>
       <c r="D18" s="3" t="inlineStr">
         <is>
-          <t>待核QS官网（仅单一来源）</t>
+          <t>待核官网介绍</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" s="2" t="inlineStr">
         <is>
-          <t>东南大学</t>
+          <t>北京师范大学</t>
         </is>
       </c>
       <c r="B19" s="2" t="inlineStr">
         <is>
-          <t>第4张排名卡</t>
+          <t>王牌专业</t>
         </is>
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>第二轮双一流建设学科12个（第三方逐项计数）</t>
+          <t>教育学、心理学、汉语言文学、数学与应用数学、地理科学、戏剧影视文学</t>
         </is>
       </c>
       <c r="D19" s="3" t="inlineStr">
         <is>
-          <t>待核教育部名单原文</t>
+          <t>待核当年招生专业目录</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" s="2" t="inlineStr">
         <is>
-          <t>东南大学</t>
+          <t>北京师范大学</t>
         </is>
       </c>
       <c r="B20" s="2" t="inlineStr">
         <is>
-          <t>王牌专业</t>
+          <t>校园风物</t>
         </is>
       </c>
       <c r="C20" s="2" t="inlineStr">
         <is>
-          <t>建筑学、土木工程、交通工程、电子科学与技术、信息工程、生物医学工程</t>
+          <t>木铎：校园标志，寓意教化；主楼：北京校区地标建筑；珠海校区：南国海滨的校区</t>
         </is>
       </c>
       <c r="D20" s="3" t="inlineStr">
         <is>
-          <t>待核当年招生专业目录</t>
+          <t>待核官网介绍</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" s="2" t="inlineStr">
         <is>
-          <t>东南大学</t>
+          <t>天津大学</t>
         </is>
       </c>
       <c r="B21" s="2" t="inlineStr">
         <is>
-          <t>深造率</t>
+          <t>王牌专业</t>
         </is>
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>B方案：学校招生宣传称近年毕业生去往华为、国家电网等重要行业和领域就业的比例高达80%（非单届统计）；中国电科为2025春招重点单位</t>
+          <t>化学工程与工艺、建筑学、测控技术与仪器、材料科学与工程、能源与动力工程、港口航道与海岸工程</t>
         </is>
       </c>
       <c r="D21" s="3" t="inlineStr">
         <is>
-          <t>待核（学校宣传口径）</t>
+          <t>待核当年招生专业目录</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" s="2" t="inlineStr">
         <is>
-          <t>东南大学</t>
+          <t>天津大学</t>
         </is>
       </c>
       <c r="B22" s="2" t="inlineStr">
         <is>
-          <t>就业方向</t>
+          <t>校园风物</t>
         </is>
       </c>
       <c r="C22" s="2" t="inlineStr">
         <is>
-          <t>华为、国家电网、中国电科</t>
+          <t>北洋园校区：海河教育园区新校区；敬业湖：卫津路校区中心湖；卫津路校区：与南开大学一路之隔</t>
         </is>
       </c>
       <c r="D22" s="3" t="inlineStr">
         <is>
-          <t>待核就业质量报告</t>
+          <t>待核官网介绍</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" s="2" t="inlineStr">
         <is>
-          <t>东南大学</t>
+          <t>南开大学</t>
         </is>
       </c>
       <c r="B23" s="2" t="inlineStr">
         <is>
-          <t>校园风物</t>
+          <t>王牌专业</t>
         </is>
       </c>
       <c r="C23" s="2" t="inlineStr">
         <is>
-          <t>大礼堂：四牌楼校区标志，原中央大学礼堂；六朝松：校园里的千年古柏；九龙湖校区：江宁主校区</t>
+          <t>数学与应用数学、化学、统计学、金融学、经济学、历史学</t>
         </is>
       </c>
       <c r="D23" s="3" t="inlineStr">
         <is>
-          <t>待核官网介绍</t>
+          <t>待核当年招生专业目录</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" s="2" t="inlineStr">
         <is>
-          <t>东南大学</t>
+          <t>南开大学</t>
         </is>
       </c>
       <c r="B24" s="2" t="inlineStr">
         <is>
-          <t>选科要求</t>
+          <t>校园风物</t>
         </is>
       </c>
       <c r="C24" s="2" t="inlineStr">
         <is>
-          <t>理工类专业：物理 + 化学；人文社科类：要求较宽，以当年招生章程为准</t>
+          <t>马蹄湖：湖畔立有周恩来总理像；新开湖：八里台校区中心湖；津南校区：海河教育园区新校区</t>
         </is>
       </c>
       <c r="D24" s="3" t="inlineStr">
         <is>
-          <t>待核2027年招生章程</t>
-        </is>
-      </c>
-    </row>
-    <row r="25">
-      <c r="A25" s="2" t="inlineStr">
-        <is>
-          <t>四川大学</t>
-        </is>
-      </c>
-      <c r="B25" s="2" t="inlineStr">
-        <is>
-          <t>第4张排名卡</t>
-        </is>
-      </c>
-      <c r="C25" s="2" t="inlineStr">
-        <is>
-          <t>第二轮双一流建设学科6个（第三方逐项计数）</t>
-        </is>
-      </c>
-      <c r="D25" s="3" t="inlineStr">
-        <is>
-          <t>待核教育部名单原文</t>
-        </is>
-      </c>
-    </row>
-    <row r="26">
-      <c r="A26" s="2" t="inlineStr">
-        <is>
-          <t>四川大学</t>
-        </is>
-      </c>
-      <c r="B26" s="2" t="inlineStr">
-        <is>
-          <t>王牌专业</t>
-        </is>
-      </c>
-      <c r="C26" s="2" t="inlineStr">
-        <is>
-          <t>口腔医学、临床医学、数学与应用数学、化学、材料科学与工程、汉语言文学</t>
-        </is>
-      </c>
-      <c r="D26" s="3" t="inlineStr">
-        <is>
-          <t>待核当年招生专业目录</t>
-        </is>
-      </c>
-    </row>
-    <row r="27">
-      <c r="A27" s="2" t="inlineStr">
-        <is>
-          <t>四川大学</t>
-        </is>
-      </c>
-      <c r="B27" s="2" t="inlineStr">
-        <is>
-          <t>深造率</t>
-        </is>
-      </c>
-      <c r="C27" s="2" t="inlineStr">
-        <is>
-          <t>B方案：多篇文章称超过55%毕业生留在西部、约43%留在成都；2021届官方报告西部就业约六成；成飞、华为、国家电网、华西医院为重点招聘单位</t>
-        </is>
-      </c>
-      <c r="D27" s="3" t="inlineStr">
-        <is>
-          <t>待核（第三方口径）</t>
-        </is>
-      </c>
-    </row>
-    <row r="28">
-      <c r="A28" s="2" t="inlineStr">
-        <is>
-          <t>四川大学</t>
-        </is>
-      </c>
-      <c r="B28" s="2" t="inlineStr">
-        <is>
-          <t>就业方向</t>
-        </is>
-      </c>
-      <c r="C28" s="2" t="inlineStr">
-        <is>
-          <t>华西医院、成飞、国家电网</t>
-        </is>
-      </c>
-      <c r="D28" s="3" t="inlineStr">
-        <is>
-          <t>待核就业质量报告</t>
-        </is>
-      </c>
-    </row>
-    <row r="29">
-      <c r="A29" s="2" t="inlineStr">
-        <is>
-          <t>四川大学</t>
-        </is>
-      </c>
-      <c r="B29" s="2" t="inlineStr">
-        <is>
-          <t>校园风物</t>
-        </is>
-      </c>
-      <c r="C29" s="2" t="inlineStr">
-        <is>
-          <t>华西钟楼：华西坝百年钟楼；明远湖：江安校区中心湖；望江校区：锦江之滨的老校区</t>
-        </is>
-      </c>
-      <c r="D29" s="3" t="inlineStr">
-        <is>
           <t>待核官网介绍</t>
-        </is>
-      </c>
-    </row>
-    <row r="30">
-      <c r="A30" s="2" t="inlineStr">
-        <is>
-          <t>四川大学</t>
-        </is>
-      </c>
-      <c r="B30" s="2" t="inlineStr">
-        <is>
-          <t>选科要求</t>
-        </is>
-      </c>
-      <c r="C30" s="2" t="inlineStr">
-        <is>
-          <t>理工医类专业：物理 + 化学；人文社科类：要求较宽，以当年招生章程为准</t>
-        </is>
-      </c>
-      <c r="D30" s="3" t="inlineStr">
-        <is>
-          <t>待核2027年招生章程</t>
-        </is>
-      </c>
-    </row>
-    <row r="31">
-      <c r="A31" s="2" t="inlineStr">
-        <is>
-          <t>中国人民大学</t>
-        </is>
-      </c>
-      <c r="B31" s="2" t="inlineStr">
-        <is>
-          <t>王牌专业</t>
-        </is>
-      </c>
-      <c r="C31" s="2" t="inlineStr">
-        <is>
-          <t>经济学、金融学、法学、新闻学、统计学、工商管理</t>
-        </is>
-      </c>
-      <c r="D31" s="3" t="inlineStr">
-        <is>
-          <t>待核当年招生专业目录</t>
-        </is>
-      </c>
-    </row>
-    <row r="32">
-      <c r="A32" s="2" t="inlineStr">
-        <is>
-          <t>中国人民大学</t>
-        </is>
-      </c>
-      <c r="B32" s="2" t="inlineStr">
-        <is>
-          <t>就业方向</t>
-        </is>
-      </c>
-      <c r="C32" s="2" t="inlineStr">
-        <is>
-          <t>外交部等党政机关、工商银行、中国银行、大型国企与知名民企</t>
-        </is>
-      </c>
-      <c r="D32" s="3" t="inlineStr">
-        <is>
-          <t>待核就业质量报告</t>
-        </is>
-      </c>
-    </row>
-    <row r="33">
-      <c r="A33" s="2" t="inlineStr">
-        <is>
-          <t>中国人民大学</t>
-        </is>
-      </c>
-      <c r="B33" s="2" t="inlineStr">
-        <is>
-          <t>校园风物</t>
-        </is>
-      </c>
-      <c r="C33" s="2" t="inlineStr">
-        <is>
-          <t>实事求是石：刻有校训的标志石；明德楼：人大标志性建筑群；通州校区：城市副中心新校区</t>
-        </is>
-      </c>
-      <c r="D33" s="3" t="inlineStr">
-        <is>
-          <t>待核官网介绍</t>
-        </is>
-      </c>
-    </row>
-    <row r="34">
-      <c r="A34" s="2" t="inlineStr">
-        <is>
-          <t>中国人民大学</t>
-        </is>
-      </c>
-      <c r="B34" s="2" t="inlineStr">
-        <is>
-          <t>选科要求</t>
-        </is>
-      </c>
-      <c r="C34" s="2" t="inlineStr">
-        <is>
-          <t>理工类专业：物理 + 化学；人文社科类：要求较宽，以当年招生章程为准</t>
-        </is>
-      </c>
-      <c r="D34" s="3" t="inlineStr">
-        <is>
-          <t>待核2027年招生章程</t>
-        </is>
-      </c>
-    </row>
-    <row r="35">
-      <c r="A35" s="2" t="inlineStr">
-        <is>
-          <t>同济大学</t>
-        </is>
-      </c>
-      <c r="B35" s="2" t="inlineStr">
-        <is>
-          <t>第4张排名卡</t>
-        </is>
-      </c>
-      <c r="C35" s="2" t="inlineStr">
-        <is>
-          <t>第二轮双一流建设学科8个（第三方逐项计数）</t>
-        </is>
-      </c>
-      <c r="D35" s="3" t="inlineStr">
-        <is>
-          <t>待核教育部名单原文</t>
-        </is>
-      </c>
-    </row>
-    <row r="36">
-      <c r="A36" s="2" t="inlineStr">
-        <is>
-          <t>同济大学</t>
-        </is>
-      </c>
-      <c r="B36" s="2" t="inlineStr">
-        <is>
-          <t>王牌专业</t>
-        </is>
-      </c>
-      <c r="C36" s="2" t="inlineStr">
-        <is>
-          <t>建筑学、城乡规划、土木工程、车辆工程、环境工程、工业设计</t>
-        </is>
-      </c>
-      <c r="D36" s="3" t="inlineStr">
-        <is>
-          <t>待核当年招生专业目录</t>
-        </is>
-      </c>
-    </row>
-    <row r="37">
-      <c r="A37" s="2" t="inlineStr">
-        <is>
-          <t>同济大学</t>
-        </is>
-      </c>
-      <c r="B37" s="2" t="inlineStr">
-        <is>
-          <t>就业方向</t>
-        </is>
-      </c>
-      <c r="C37" s="2" t="inlineStr">
-        <is>
-          <t>建筑设计与城市规划、土木交通工程、汽车与先进制造</t>
-        </is>
-      </c>
-      <c r="D37" s="3" t="inlineStr">
-        <is>
-          <t>待核就业质量报告</t>
-        </is>
-      </c>
-    </row>
-    <row r="38">
-      <c r="A38" s="2" t="inlineStr">
-        <is>
-          <t>同济大学</t>
-        </is>
-      </c>
-      <c r="B38" s="2" t="inlineStr">
-        <is>
-          <t>校园风物</t>
-        </is>
-      </c>
-      <c r="C38" s="2" t="inlineStr">
-        <is>
-          <t>文远楼（1953年建，常被称为中国第一座包豪斯风格建筑）；大礼堂（1962年建，大跨度拱形结构）</t>
-        </is>
-      </c>
-      <c r="D38" s="3" t="inlineStr">
-        <is>
-          <t>待核官网介绍</t>
-        </is>
-      </c>
-    </row>
-    <row r="39">
-      <c r="A39" s="2" t="inlineStr">
-        <is>
-          <t>同济大学</t>
-        </is>
-      </c>
-      <c r="B39" s="2" t="inlineStr">
-        <is>
-          <t>选科要求</t>
-        </is>
-      </c>
-      <c r="C39" s="2" t="inlineStr">
-        <is>
-          <t>理工类专业：物理 + 化学；人文社科类：要求较宽，以当年招生章程为准</t>
-        </is>
-      </c>
-      <c r="D39" s="3" t="inlineStr">
-        <is>
-          <t>待核2027年招生章程</t>
-        </is>
-      </c>
-    </row>
-    <row r="40">
-      <c r="A40" s="2" t="inlineStr">
-        <is>
-          <t>北京师范大学</t>
-        </is>
-      </c>
-      <c r="B40" s="2" t="inlineStr">
-        <is>
-          <t>王牌专业</t>
-        </is>
-      </c>
-      <c r="C40" s="2" t="inlineStr">
-        <is>
-          <t>教育学、心理学、汉语言文学、数学与应用数学、地理科学、戏剧影视文学</t>
-        </is>
-      </c>
-      <c r="D40" s="3" t="inlineStr">
-        <is>
-          <t>待核当年招生专业目录</t>
-        </is>
-      </c>
-    </row>
-    <row r="41">
-      <c r="A41" s="2" t="inlineStr">
-        <is>
-          <t>北京师范大学</t>
-        </is>
-      </c>
-      <c r="B41" s="2" t="inlineStr">
-        <is>
-          <t>就业方向</t>
-        </is>
-      </c>
-      <c r="C41" s="2" t="inlineStr">
-        <is>
-          <t>教育与科研、文化传媒、党政机关与国企</t>
-        </is>
-      </c>
-      <c r="D41" s="3" t="inlineStr">
-        <is>
-          <t>待核就业质量报告</t>
-        </is>
-      </c>
-    </row>
-    <row r="42">
-      <c r="A42" s="2" t="inlineStr">
-        <is>
-          <t>北京师范大学</t>
-        </is>
-      </c>
-      <c r="B42" s="2" t="inlineStr">
-        <is>
-          <t>校园风物</t>
-        </is>
-      </c>
-      <c r="C42" s="2" t="inlineStr">
-        <is>
-          <t>木铎：校园标志，寓意教化；主楼：北京校区地标建筑；珠海校区：南国海滨的校区</t>
-        </is>
-      </c>
-      <c r="D42" s="3" t="inlineStr">
-        <is>
-          <t>待核官网介绍</t>
-        </is>
-      </c>
-    </row>
-    <row r="43">
-      <c r="A43" s="2" t="inlineStr">
-        <is>
-          <t>北京师范大学</t>
-        </is>
-      </c>
-      <c r="B43" s="2" t="inlineStr">
-        <is>
-          <t>选科要求</t>
-        </is>
-      </c>
-      <c r="C43" s="2" t="inlineStr">
-        <is>
-          <t>理工类专业：物理 + 化学；人文社科类：要求较宽，以当年招生章程为准</t>
-        </is>
-      </c>
-      <c r="D43" s="3" t="inlineStr">
-        <is>
-          <t>待核2027年招生章程</t>
-        </is>
-      </c>
-    </row>
-    <row r="44">
-      <c r="A44" s="2" t="inlineStr">
-        <is>
-          <t>天津大学</t>
-        </is>
-      </c>
-      <c r="B44" s="2" t="inlineStr">
-        <is>
-          <t>王牌专业</t>
-        </is>
-      </c>
-      <c r="C44" s="2" t="inlineStr">
-        <is>
-          <t>化学工程与工艺、建筑学、测控技术与仪器、材料科学与工程、能源与动力工程、港口航道与海岸工程</t>
-        </is>
-      </c>
-      <c r="D44" s="3" t="inlineStr">
-        <is>
-          <t>待核当年招生专业目录</t>
-        </is>
-      </c>
-    </row>
-    <row r="45">
-      <c r="A45" s="2" t="inlineStr">
-        <is>
-          <t>天津大学</t>
-        </is>
-      </c>
-      <c r="B45" s="2" t="inlineStr">
-        <is>
-          <t>就业方向</t>
-        </is>
-      </c>
-      <c r="C45" s="2" t="inlineStr">
-        <is>
-          <t>化工与能源、建筑与土木工程、电子信息与制造</t>
-        </is>
-      </c>
-      <c r="D45" s="3" t="inlineStr">
-        <is>
-          <t>待核就业质量报告</t>
-        </is>
-      </c>
-    </row>
-    <row r="46">
-      <c r="A46" s="2" t="inlineStr">
-        <is>
-          <t>天津大学</t>
-        </is>
-      </c>
-      <c r="B46" s="2" t="inlineStr">
-        <is>
-          <t>校园风物</t>
-        </is>
-      </c>
-      <c r="C46" s="2" t="inlineStr">
-        <is>
-          <t>北洋园校区：海河教育园区新校区；敬业湖：卫津路校区中心湖；卫津路校区：与南开大学一路之隔</t>
-        </is>
-      </c>
-      <c r="D46" s="3" t="inlineStr">
-        <is>
-          <t>待核官网介绍</t>
-        </is>
-      </c>
-    </row>
-    <row r="47">
-      <c r="A47" s="2" t="inlineStr">
-        <is>
-          <t>天津大学</t>
-        </is>
-      </c>
-      <c r="B47" s="2" t="inlineStr">
-        <is>
-          <t>选科要求</t>
-        </is>
-      </c>
-      <c r="C47" s="2" t="inlineStr">
-        <is>
-          <t>理工类专业：物理 + 化学；人文社科类：要求较宽，以当年招生章程为准</t>
-        </is>
-      </c>
-      <c r="D47" s="3" t="inlineStr">
-        <is>
-          <t>待核2027年招生章程</t>
-        </is>
-      </c>
-    </row>
-    <row r="48">
-      <c r="A48" s="2" t="inlineStr">
-        <is>
-          <t>南开大学</t>
-        </is>
-      </c>
-      <c r="B48" s="2" t="inlineStr">
-        <is>
-          <t>王牌专业</t>
-        </is>
-      </c>
-      <c r="C48" s="2" t="inlineStr">
-        <is>
-          <t>数学与应用数学、化学、统计学、金融学、经济学、历史学</t>
-        </is>
-      </c>
-      <c r="D48" s="3" t="inlineStr">
-        <is>
-          <t>待核当年招生专业目录</t>
-        </is>
-      </c>
-    </row>
-    <row r="49">
-      <c r="A49" s="2" t="inlineStr">
-        <is>
-          <t>南开大学</t>
-        </is>
-      </c>
-      <c r="B49" s="2" t="inlineStr">
-        <is>
-          <t>就业方向</t>
-        </is>
-      </c>
-      <c r="C49" s="2" t="inlineStr">
-        <is>
-          <t>金融与经济、科研院所与高校、党政机关与国企</t>
-        </is>
-      </c>
-      <c r="D49" s="3" t="inlineStr">
-        <is>
-          <t>待核就业质量报告</t>
-        </is>
-      </c>
-    </row>
-    <row r="50">
-      <c r="A50" s="2" t="inlineStr">
-        <is>
-          <t>南开大学</t>
-        </is>
-      </c>
-      <c r="B50" s="2" t="inlineStr">
-        <is>
-          <t>校园风物</t>
-        </is>
-      </c>
-      <c r="C50" s="2" t="inlineStr">
-        <is>
-          <t>马蹄湖：湖畔立有周恩来总理像；新开湖：八里台校区中心湖；津南校区：海河教育园区新校区</t>
-        </is>
-      </c>
-      <c r="D50" s="3" t="inlineStr">
-        <is>
-          <t>待核官网介绍</t>
-        </is>
-      </c>
-    </row>
-    <row r="51">
-      <c r="A51" s="2" t="inlineStr">
-        <is>
-          <t>南开大学</t>
-        </is>
-      </c>
-      <c r="B51" s="2" t="inlineStr">
-        <is>
-          <t>选科要求</t>
-        </is>
-      </c>
-      <c r="C51" s="2" t="inlineStr">
-        <is>
-          <t>理工类专业：物理 + 化学；人文社科类：要求较宽，以当年招生章程为准</t>
-        </is>
-      </c>
-      <c r="D51" s="3" t="inlineStr">
-        <is>
-          <t>待核2027年招生章程</t>
         </is>
       </c>
     </row>
@@ -2135,9 +1541,9 @@
           <t>就业质量报告、公开报道，概括整理</t>
         </is>
       </c>
-      <c r="F17" s="3" t="inlineStr">
-        <is>
-          <t>待核就业质量报告</t>
+      <c r="F17" s="2" t="inlineStr">
+        <is>
+          <t>运营概括（行业方向，非统计数据）</t>
         </is>
       </c>
     </row>
@@ -2260,12 +1666,12 @@
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>分省招生计划、招生章程</t>
-        </is>
-      </c>
-      <c r="F21" s="3" t="inlineStr">
-        <is>
-          <t>待核2027年招生章程</t>
+          <t>教育部《普通高校本科招生专业选考科目要求指引（通用版）》、招生章程</t>
+        </is>
+      </c>
+      <c r="F21" s="2" t="inlineStr">
+        <is>
+          <t>较可靠（符合教育部选科指引：理工医农类原则上物理+化学）；具体专业以2027年招生章程为准</t>
         </is>
       </c>
     </row>
@@ -2893,9 +2299,9 @@
           <t>就业质量报告、公开报道，概括整理</t>
         </is>
       </c>
-      <c r="F17" s="3" t="inlineStr">
-        <is>
-          <t>待核就业质量报告</t>
+      <c r="F17" s="2" t="inlineStr">
+        <is>
+          <t>运营概括（行业方向，非统计数据）</t>
         </is>
       </c>
     </row>
@@ -3018,12 +2424,12 @@
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>分省招生计划、招生章程</t>
-        </is>
-      </c>
-      <c r="F21" s="3" t="inlineStr">
-        <is>
-          <t>待核2027年招生章程</t>
+          <t>教育部《普通高校本科招生专业选考科目要求指引（通用版）》、招生章程</t>
+        </is>
+      </c>
+      <c r="F21" s="2" t="inlineStr">
+        <is>
+          <t>较可靠（符合教育部选科指引：理工医农类原则上物理+化学）；具体专业以2027年招生章程为准</t>
         </is>
       </c>
     </row>
@@ -3360,12 +2766,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>xuanxiao.org 院校页（单一第三方来源）</t>
-        </is>
-      </c>
-      <c r="F8" s="3" t="inlineStr">
-        <is>
-          <t>待核QS官网（仅单一来源）</t>
+          <t>新东方QS2027 TOP500完整版、xuanxiao.org（两源一致）</t>
+        </is>
+      </c>
+      <c r="F8" s="2" t="inlineStr">
+        <is>
+          <t>较可靠（两源一致），待核QS官网</t>
         </is>
       </c>
     </row>
@@ -3651,9 +3057,9 @@
           <t>就业质量报告、公开报道，概括整理</t>
         </is>
       </c>
-      <c r="F17" s="3" t="inlineStr">
-        <is>
-          <t>待核就业质量报告</t>
+      <c r="F17" s="2" t="inlineStr">
+        <is>
+          <t>运营概括（行业方向，非统计数据）</t>
         </is>
       </c>
     </row>
@@ -3670,7 +3076,7 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
-          <t>戚发轫（北京航空学院首届学生）；陈懋章（北航首届学生，院士）；罗阳（北京航空学院1982届，歼-15研制现场总指挥）</t>
+          <t>戚发轫、陈懋章（北京航空学院首届学生）；罗阳（1982年北京航空学院毕业，歼-15研制现场总指挥）</t>
         </is>
       </c>
       <c r="D18" s="2" t="inlineStr">
@@ -3683,9 +3089,9 @@
           <t>学校官网、权威媒体</t>
         </is>
       </c>
-      <c r="F18" s="3" t="inlineStr">
-        <is>
-          <t>待核（罗阳学籍）</t>
+      <c r="F18" s="2" t="inlineStr">
+        <is>
+          <t>已核</t>
         </is>
       </c>
     </row>
@@ -3776,12 +3182,12 @@
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>分省招生计划、招生章程</t>
-        </is>
-      </c>
-      <c r="F21" s="3" t="inlineStr">
-        <is>
-          <t>待核2027年招生章程</t>
+          <t>教育部《普通高校本科招生专业选考科目要求指引（通用版）》、招生章程</t>
+        </is>
+      </c>
+      <c r="F21" s="2" t="inlineStr">
+        <is>
+          <t>较可靠（符合教育部选科指引：理工医农类原则上物理+化学）；具体专业以2027年招生章程为准</t>
         </is>
       </c>
     </row>
@@ -4409,9 +3815,9 @@
           <t>就业质量报告、公开报道，概括整理</t>
         </is>
       </c>
-      <c r="F17" s="3" t="inlineStr">
-        <is>
-          <t>待核就业质量报告</t>
+      <c r="F17" s="2" t="inlineStr">
+        <is>
+          <t>运营概括（行业方向，非统计数据）</t>
         </is>
       </c>
     </row>
@@ -4534,12 +3940,12 @@
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>分省招生计划、招生章程</t>
-        </is>
-      </c>
-      <c r="F21" s="3" t="inlineStr">
-        <is>
-          <t>待核2027年招生章程</t>
+          <t>教育部《普通高校本科招生专业选考科目要求指引（通用版）》、招生章程</t>
+        </is>
+      </c>
+      <c r="F21" s="2" t="inlineStr">
+        <is>
+          <t>较可靠（符合教育部选科指引：理工医农类原则上物理+化学）；具体专业以2027年招生章程为准</t>
         </is>
       </c>
     </row>
@@ -5167,9 +4573,9 @@
           <t>就业质量报告、公开报道，概括整理</t>
         </is>
       </c>
-      <c r="F17" s="3" t="inlineStr">
-        <is>
-          <t>待核就业质量报告</t>
+      <c r="F17" s="2" t="inlineStr">
+        <is>
+          <t>运营概括（行业方向，非统计数据）</t>
         </is>
       </c>
     </row>
@@ -5186,12 +4592,12 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
-          <t>罗俊（1985年获中山大学理学硕士）；许宁生（中山大学物理系校友）；黄达人（中山大学数学系校友、原校长）</t>
+          <t>罗俊（中山大学理学硕士）；许宁生（1982年中山大学物理系）；黄达人本科研究生均为浙江大学，非中大校友，已撤下</t>
         </is>
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>罗俊 中国科学院院士；许宁生 中国科学院院士；黄达人 中山大学原校长</t>
+          <t>罗俊 中国科学院院士；许宁生 中国科学院院士</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
@@ -5199,9 +4605,9 @@
           <t>学校官网、权威媒体</t>
         </is>
       </c>
-      <c r="F18" s="3" t="inlineStr">
-        <is>
-          <t>待核（许宁生、黄达人学籍）</t>
+      <c r="F18" s="2" t="inlineStr">
+        <is>
+          <t>已核（已更正）</t>
         </is>
       </c>
     </row>
@@ -5292,12 +4698,12 @@
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>分省招生计划、招生章程</t>
-        </is>
-      </c>
-      <c r="F21" s="3" t="inlineStr">
-        <is>
-          <t>待核2027年招生章程</t>
+          <t>教育部《普通高校本科招生专业选考科目要求指引（通用版）》、招生章程</t>
+        </is>
+      </c>
+      <c r="F21" s="2" t="inlineStr">
+        <is>
+          <t>较可靠（符合教育部选科指引：理工医农类原则上物理+化学）；具体专业以2027年招生章程为准</t>
         </is>
       </c>
     </row>
@@ -5634,12 +5040,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>xuanxiao.org 院校页（单一第三方来源）</t>
-        </is>
-      </c>
-      <c r="F8" s="3" t="inlineStr">
-        <is>
-          <t>待核QS官网（仅单一来源）</t>
+          <t>新东方QS2027 TOP500完整版、xuanxiao.org（两源一致）</t>
+        </is>
+      </c>
+      <c r="F8" s="2" t="inlineStr">
+        <is>
+          <t>较可靠（两源一致），待核QS官网</t>
         </is>
       </c>
     </row>
@@ -5688,7 +5094,7 @@
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
-          <t>第二轮双一流建设学科12个（第三方逐项计数）</t>
+          <t>第二轮双一流建设学科12个（逐项核对教育部名单）</t>
         </is>
       </c>
       <c r="D10" s="2" t="inlineStr">
@@ -5701,9 +5107,9 @@
           <t>教育部 教研函〔2022〕1号 名单（转载）</t>
         </is>
       </c>
-      <c r="F10" s="3" t="inlineStr">
-        <is>
-          <t>待核教育部名单原文</t>
+      <c r="F10" s="2" t="inlineStr">
+        <is>
+          <t>已核</t>
         </is>
       </c>
     </row>
@@ -5925,9 +5331,9 @@
           <t>就业质量报告、公开报道，概括整理</t>
         </is>
       </c>
-      <c r="F17" s="3" t="inlineStr">
-        <is>
-          <t>待核就业质量报告</t>
+      <c r="F17" s="2" t="inlineStr">
+        <is>
+          <t>运营概括（行业方向，非统计数据）</t>
         </is>
       </c>
     </row>
@@ -6050,12 +5456,12 @@
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>分省招生计划、招生章程</t>
-        </is>
-      </c>
-      <c r="F21" s="3" t="inlineStr">
-        <is>
-          <t>待核2027年招生章程</t>
+          <t>教育部《普通高校本科招生专业选考科目要求指引（通用版）》、招生章程</t>
+        </is>
+      </c>
+      <c r="F21" s="2" t="inlineStr">
+        <is>
+          <t>较可靠（符合教育部选科指引：理工医农类原则上物理+化学）；具体专业以2027年招生章程为准</t>
         </is>
       </c>
     </row>
@@ -6446,7 +5852,7 @@
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
-          <t>第二轮双一流建设学科6个（第三方逐项计数）</t>
+          <t>第二轮双一流建设学科6个：数学、化学、材料科学与工程、基础医学、口腔医学、护理学</t>
         </is>
       </c>
       <c r="D10" s="2" t="inlineStr">
@@ -6459,9 +5865,9 @@
           <t>教育部 教研函〔2022〕1号 名单（转载）</t>
         </is>
       </c>
-      <c r="F10" s="3" t="inlineStr">
-        <is>
-          <t>待核教育部名单原文</t>
+      <c r="F10" s="2" t="inlineStr">
+        <is>
+          <t>已核</t>
         </is>
       </c>
     </row>
@@ -6683,9 +6089,9 @@
           <t>就业质量报告、公开报道，概括整理</t>
         </is>
       </c>
-      <c r="F17" s="3" t="inlineStr">
-        <is>
-          <t>待核就业质量报告</t>
+      <c r="F17" s="2" t="inlineStr">
+        <is>
+          <t>运营概括（行业方向，非统计数据）</t>
         </is>
       </c>
     </row>
@@ -6808,12 +6214,12 @@
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>分省招生计划、招生章程</t>
-        </is>
-      </c>
-      <c r="F21" s="3" t="inlineStr">
-        <is>
-          <t>待核2027年招生章程</t>
+          <t>教育部《普通高校本科招生专业选考科目要求指引（通用版）》、招生章程</t>
+        </is>
+      </c>
+      <c r="F21" s="2" t="inlineStr">
+        <is>
+          <t>较可靠（符合教育部选科指引：理工医农类原则上物理+化学）；具体专业以2027年招生章程为准</t>
         </is>
       </c>
     </row>
@@ -7441,9 +6847,9 @@
           <t>就业质量报告、公开报道，概括整理</t>
         </is>
       </c>
-      <c r="F17" s="3" t="inlineStr">
-        <is>
-          <t>待核就业质量报告</t>
+      <c r="F17" s="2" t="inlineStr">
+        <is>
+          <t>运营概括（行业方向，非统计数据）</t>
         </is>
       </c>
     </row>
@@ -7566,12 +6972,12 @@
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>分省招生计划、招生章程</t>
-        </is>
-      </c>
-      <c r="F21" s="3" t="inlineStr">
-        <is>
-          <t>待核2027年招生章程</t>
+          <t>教育部《普通高校本科招生专业选考科目要求指引（通用版）》、招生章程</t>
+        </is>
+      </c>
+      <c r="F21" s="2" t="inlineStr">
+        <is>
+          <t>较可靠（符合教育部选科指引：理工医农类原则上物理+化学）；具体专业以2027年招生章程为准</t>
         </is>
       </c>
     </row>
@@ -7962,7 +7368,7 @@
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
-          <t>第二轮双一流建设学科8个（第三方逐项计数）</t>
+          <t>第二轮双一流建设学科8个：生物学、建筑学、土木工程、测绘科学与技术、环境科学与工程、城乡规划学、风景园林学、设计学</t>
         </is>
       </c>
       <c r="D10" s="2" t="inlineStr">
@@ -7975,9 +7381,9 @@
           <t>教育部 教研函〔2022〕1号 名单（转载）</t>
         </is>
       </c>
-      <c r="F10" s="3" t="inlineStr">
-        <is>
-          <t>待核教育部名单原文</t>
+      <c r="F10" s="2" t="inlineStr">
+        <is>
+          <t>已核</t>
         </is>
       </c>
     </row>
@@ -8199,9 +7605,9 @@
           <t>就业质量报告、公开报道，概括整理</t>
         </is>
       </c>
-      <c r="F17" s="3" t="inlineStr">
-        <is>
-          <t>待核就业质量报告</t>
+      <c r="F17" s="2" t="inlineStr">
+        <is>
+          <t>运营概括（行业方向，非统计数据）</t>
         </is>
       </c>
     </row>
@@ -8324,12 +7730,12 @@
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>分省招生计划、招生章程</t>
-        </is>
-      </c>
-      <c r="F21" s="3" t="inlineStr">
-        <is>
-          <t>待核2027年招生章程</t>
+          <t>教育部《普通高校本科招生专业选考科目要求指引（通用版）》、招生章程</t>
+        </is>
+      </c>
+      <c r="F21" s="2" t="inlineStr">
+        <is>
+          <t>较可靠（符合教育部选科指引：理工医农类原则上物理+化学）；具体专业以2027年招生章程为准</t>
         </is>
       </c>
     </row>
@@ -8957,9 +8363,9 @@
           <t>就业质量报告、公开报道，概括整理</t>
         </is>
       </c>
-      <c r="F17" s="3" t="inlineStr">
-        <is>
-          <t>待核就业质量报告</t>
+      <c r="F17" s="2" t="inlineStr">
+        <is>
+          <t>运营概括（行业方向，非统计数据）</t>
         </is>
       </c>
     </row>
@@ -9082,12 +8488,12 @@
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>分省招生计划、招生章程</t>
-        </is>
-      </c>
-      <c r="F21" s="3" t="inlineStr">
-        <is>
-          <t>待核2027年招生章程</t>
+          <t>教育部《普通高校本科招生专业选考科目要求指引（通用版）》、招生章程</t>
+        </is>
+      </c>
+      <c r="F21" s="2" t="inlineStr">
+        <is>
+          <t>较可靠（符合教育部选科指引：理工医农类原则上物理+化学）；具体专业以2027年招生章程为准</t>
         </is>
       </c>
     </row>
